--- a/Spiele.xlsx
+++ b/Spiele.xlsx
@@ -475,12 +475,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -575,12 +575,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,12 +595,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -615,12 +615,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -711,12 +711,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -731,12 +731,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -751,12 +751,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -967,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,12 +987,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1047,12 +1047,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,12 +1123,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1183,12 +1183,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1203,12 +1203,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1223,12 +1223,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,12 +1243,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1379,12 +1379,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1695,12 +1695,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1911,12 +1911,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2067,12 +2067,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2127,12 +2127,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2147,12 +2147,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2223,12 +2223,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2303,12 +2303,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2419,12 +2419,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2439,12 +2439,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2479,12 +2479,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2499,12 +2499,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2519,12 +2519,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2559,12 +2559,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2655,12 +2655,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2695,12 +2695,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2775,12 +2775,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2851,12 +2851,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2871,12 +2871,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2951,12 +2951,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3011,12 +3011,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3067,12 +3067,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3087,12 +3087,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3127,12 +3127,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3207,12 +3207,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3227,12 +3227,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3303,12 +3303,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3323,12 +3323,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3343,12 +3343,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3363,12 +3363,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3383,12 +3383,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3423,12 +3423,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3443,12 +3443,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3539,12 +3539,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3559,12 +3559,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3579,12 +3579,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3619,12 +3619,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3639,12 +3639,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3715,12 +3715,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3735,12 +3735,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3775,12 +3775,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3795,12 +3795,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3815,12 +3815,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3835,12 +3835,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3855,12 +3855,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3931,12 +3931,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3951,12 +3951,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3971,12 +3971,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3991,12 +3991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4031,12 +4031,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4051,12 +4051,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4091,12 +4091,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4147,12 +4147,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4207,12 +4207,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4287,12 +4287,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4307,12 +4307,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4403,12 +4403,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4423,12 +4423,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4443,12 +4443,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4483,12 +4483,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4503,12 +4503,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4523,12 +4523,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4579,12 +4579,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4599,12 +4599,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4619,12 +4619,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4699,12 +4699,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4719,12 +4719,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4739,12 +4739,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4795,12 +4795,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4815,12 +4815,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4835,12 +4835,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4855,12 +4855,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4915,12 +4915,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4935,12 +4935,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5011,12 +5011,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5031,12 +5031,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5071,12 +5071,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5091,12 +5091,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5111,12 +5111,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5131,12 +5131,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5151,12 +5151,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5171,12 +5171,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5227,12 +5227,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5267,12 +5267,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5287,12 +5287,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5307,12 +5307,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5327,12 +5327,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5347,12 +5347,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5367,12 +5367,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5443,12 +5443,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5463,12 +5463,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5503,12 +5503,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5563,12 +5563,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5583,12 +5583,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5603,12 +5603,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5679,12 +5679,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5699,12 +5699,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5719,12 +5719,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5739,12 +5739,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5759,12 +5759,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5779,12 +5779,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5799,12 +5799,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5875,12 +5875,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5895,12 +5895,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5915,12 +5915,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5935,12 +5935,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5955,12 +5955,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5975,12 +5975,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6015,12 +6015,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6035,12 +6035,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6091,12 +6091,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6111,12 +6111,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6131,12 +6131,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6151,12 +6151,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6171,12 +6171,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6191,12 +6191,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6211,12 +6211,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6231,12 +6231,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6307,12 +6307,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6327,12 +6327,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6347,12 +6347,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6367,12 +6367,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6447,12 +6447,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6467,12 +6467,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6536,12 +6536,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6556,12 +6556,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6576,12 +6576,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6616,12 +6616,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6636,12 +6636,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6656,12 +6656,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6676,12 +6676,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6696,12 +6696,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6752,12 +6752,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6792,12 +6792,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6812,12 +6812,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6832,12 +6832,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6852,12 +6852,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6872,12 +6872,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6892,12 +6892,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6912,12 +6912,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6968,12 +6968,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6988,12 +6988,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7008,12 +7008,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7028,12 +7028,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7048,12 +7048,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7068,12 +7068,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7088,12 +7088,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7108,12 +7108,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7128,12 +7128,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7184,12 +7184,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7204,12 +7204,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7224,12 +7224,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7244,12 +7244,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7264,12 +7264,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7284,12 +7284,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7304,12 +7304,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7324,12 +7324,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7344,12 +7344,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7400,12 +7400,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7420,12 +7420,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7440,12 +7440,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7480,12 +7480,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7500,12 +7500,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7520,12 +7520,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7540,12 +7540,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7560,12 +7560,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7616,12 +7616,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayer 04 Leverkusen</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>Bayern</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7636,12 +7636,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim 1846</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7656,12 +7656,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7676,12 +7676,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7696,12 +7696,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>Bremen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. FSV Mainz 05</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7716,12 +7716,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leipzig</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7736,12 +7736,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>Gladbach</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7756,12 +7756,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7776,12 +7776,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>HSV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/Spiele.xlsx
+++ b/Spiele.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="25"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="34. Spieltag"/>
@@ -385,7 +385,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +396,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -432,10 +438,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -4744,7 +4750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -4758,7 +4764,7 @@
         <v>77275</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -4772,7 +4778,7 @@
         <v>77276</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -4786,7 +4792,7 @@
         <v>77277</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -4800,7 +4806,7 @@
         <v>77279</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -4814,7 +4820,7 @@
         <v>77280</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -4828,7 +4834,7 @@
         <v>77282</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4842,7 +4848,7 @@
         <v>77274</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -4856,7 +4862,7 @@
         <v>77281</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
